--- a/概要/【仕様フォーマット001】舞台劇.xlsx
+++ b/概要/【仕様フォーマット001】舞台劇.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="1650" yWindow="300" windowWidth="22965" windowHeight="14715" activeTab="6"/>
+    <workbookView xWindow="1650" yWindow="300" windowWidth="22965" windowHeight="14715" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="1_更新履歴" sheetId="1" r:id="rId1"/>
@@ -1440,6 +1440,13 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1467,13 +1474,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1682,14 +1682,14 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>545856</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>16852</xdr:rowOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>5646</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>212481</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>45427</xdr:rowOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>11809</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1704,8 +1704,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3300779" y="2867025"/>
-          <a:ext cx="1732817" cy="775921"/>
+          <a:off x="3280091" y="2280440"/>
+          <a:ext cx="1717302" cy="768163"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
           <a:avLst/>
@@ -1744,15 +1744,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>34070</xdr:colOff>
+      <xdr:colOff>36656</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>34803</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>16852</xdr:rowOff>
+      <xdr:colOff>37389</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>5646</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1770,8 +1770,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4166455" y="2126273"/>
-          <a:ext cx="733" cy="740752"/>
+          <a:off x="4138009" y="2122394"/>
+          <a:ext cx="733" cy="158046"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1863,13 +1863,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>34803</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>45427</xdr:rowOff>
+      <xdr:colOff>43249</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>52150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>40663</xdr:colOff>
+      <xdr:colOff>44112</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>66676</xdr:rowOff>
     </xdr:to>
@@ -1883,14 +1883,14 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="8" idx="2"/>
+          <a:stCxn id="31" idx="2"/>
           <a:endCxn id="14" idx="0"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4167188" y="3642946"/>
-          <a:ext cx="5860" cy="570768"/>
+        <a:xfrm flipH="1">
+          <a:off x="4144602" y="3996621"/>
+          <a:ext cx="863" cy="193820"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2791,6 +2791,125 @@
         <a:xfrm flipH="1">
           <a:off x="2706414" y="4736224"/>
           <a:ext cx="597776" cy="6569"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>552579</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>1164</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>219204</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>52150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="フローチャート: 処理 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BE1CB89-80C8-4310-BF9D-990DF46106A8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3286814" y="3228458"/>
+          <a:ext cx="1717302" cy="768163"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000"/>
+            <a:t>ムービー</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>37389</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>11809</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>44112</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>1164</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="32" name="直線矢印コネクタ 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DE3DE97-C6C9-13A0-C798-29EAF2DEC050}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="8" idx="2"/>
+          <a:endCxn id="31" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4138742" y="3048603"/>
+          <a:ext cx="6723" cy="179855"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -4847,18 +4966,18 @@
       <c r="P14" s="13"/>
       <c r="Q14" s="13"/>
       <c r="R14" s="13"/>
-      <c r="S14" s="102"/>
-      <c r="T14" s="103"/>
-      <c r="U14" s="103"/>
-      <c r="V14" s="103"/>
-      <c r="W14" s="103"/>
-      <c r="X14" s="103"/>
-      <c r="Y14" s="103"/>
-      <c r="Z14" s="103"/>
-      <c r="AA14" s="103"/>
-      <c r="AB14" s="103"/>
-      <c r="AC14" s="103"/>
-      <c r="AD14" s="103"/>
+      <c r="S14" s="105"/>
+      <c r="T14" s="106"/>
+      <c r="U14" s="106"/>
+      <c r="V14" s="106"/>
+      <c r="W14" s="106"/>
+      <c r="X14" s="106"/>
+      <c r="Y14" s="106"/>
+      <c r="Z14" s="106"/>
+      <c r="AA14" s="106"/>
+      <c r="AB14" s="106"/>
+      <c r="AC14" s="106"/>
+      <c r="AD14" s="106"/>
     </row>
     <row r="15" spans="1:67" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="13"/>
@@ -5056,18 +5175,18 @@
       <c r="P21" s="13"/>
       <c r="Q21" s="13"/>
       <c r="R21" s="13"/>
-      <c r="S21" s="102"/>
-      <c r="T21" s="103"/>
-      <c r="U21" s="103"/>
-      <c r="V21" s="103"/>
-      <c r="W21" s="103"/>
-      <c r="X21" s="103"/>
-      <c r="Y21" s="103"/>
-      <c r="Z21" s="103"/>
-      <c r="AA21" s="103"/>
-      <c r="AB21" s="103"/>
-      <c r="AC21" s="103"/>
-      <c r="AD21" s="103"/>
+      <c r="S21" s="105"/>
+      <c r="T21" s="106"/>
+      <c r="U21" s="106"/>
+      <c r="V21" s="106"/>
+      <c r="W21" s="106"/>
+      <c r="X21" s="106"/>
+      <c r="Y21" s="106"/>
+      <c r="Z21" s="106"/>
+      <c r="AA21" s="106"/>
+      <c r="AB21" s="106"/>
+      <c r="AC21" s="106"/>
+      <c r="AD21" s="106"/>
     </row>
     <row r="22" spans="2:51" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="13"/>
@@ -5277,9 +5396,9 @@
       <c r="E29" s="13"/>
       <c r="F29" s="13"/>
       <c r="G29" s="13"/>
-      <c r="K29" s="104"/>
-      <c r="L29" s="103"/>
-      <c r="M29" s="103"/>
+      <c r="K29" s="107"/>
+      <c r="L29" s="106"/>
+      <c r="M29" s="106"/>
       <c r="S29" s="13"/>
       <c r="T29" s="13"/>
       <c r="U29" s="13"/>
@@ -5647,8 +5766,8 @@
       <c r="AY36" s="13"/>
     </row>
     <row r="37" spans="2:51" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="105"/>
-      <c r="D37" s="103"/>
+      <c r="C37" s="108"/>
+      <c r="D37" s="106"/>
       <c r="E37" s="13"/>
       <c r="F37" s="13"/>
       <c r="G37" s="13"/>
@@ -10172,52 +10291,52 @@
       <c r="C6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="96" t="s">
+      <c r="D6" s="99" t="s">
         <v>87</v>
       </c>
       <c r="F6" s="89"/>
     </row>
     <row r="7" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="7"/>
-      <c r="D7" s="98"/>
+      <c r="D7" s="101"/>
       <c r="F7" s="89"/>
     </row>
     <row r="8" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C8" s="99" t="s">
+      <c r="C8" s="102" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="96" t="s">
+      <c r="D8" s="99" t="s">
         <v>62</v>
       </c>
       <c r="F8" s="89"/>
     </row>
     <row r="9" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C9" s="100"/>
-      <c r="D9" s="97"/>
+      <c r="C9" s="103"/>
+      <c r="D9" s="100"/>
     </row>
     <row r="10" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C10" s="101"/>
-      <c r="D10" s="98"/>
+      <c r="C10" s="104"/>
+      <c r="D10" s="101"/>
     </row>
     <row r="11" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C11" s="99" t="s">
+      <c r="C11" s="102" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="96" t="s">
+      <c r="D11" s="99" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C12" s="100"/>
-      <c r="D12" s="97"/>
+      <c r="C12" s="103"/>
+      <c r="D12" s="100"/>
     </row>
     <row r="13" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C13" s="100"/>
-      <c r="D13" s="97"/>
+      <c r="C13" s="103"/>
+      <c r="D13" s="100"/>
     </row>
     <row r="14" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C14" s="101"/>
-      <c r="D14" s="98"/>
+      <c r="C14" s="104"/>
+      <c r="D14" s="101"/>
     </row>
     <row r="15" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="16" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -10249,7 +10368,7 @@
     </row>
     <row r="23" spans="3:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="24" spans="3:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D24" s="107" t="s">
+      <c r="D24" s="97" t="s">
         <v>93</v>
       </c>
     </row>
@@ -10275,7 +10394,7 @@
       </c>
     </row>
     <row r="30" spans="3:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C30" s="106" t="s">
+      <c r="C30" s="96" t="s">
         <v>98</v>
       </c>
       <c r="D30" s="89" t="s">
@@ -10288,7 +10407,7 @@
       </c>
     </row>
     <row r="32" spans="3:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C32" s="106" t="s">
+      <c r="C32" s="96" t="s">
         <v>99</v>
       </c>
       <c r="D32" s="89" t="s">
@@ -10296,7 +10415,7 @@
       </c>
     </row>
     <row r="33" spans="4:4" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D33" s="108" t="s">
+      <c r="D33" s="98" t="s">
         <v>102</v>
       </c>
     </row>
@@ -19050,6 +19169,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100A6A6C361903FA540AF4D79E6EA2B777C" ma:contentTypeVersion="18" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="ea7c12cc56e366ff4dda5c6e96eadaab">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="aaa52e1c-8772-4366-aa63-bf636c80ebd4" xmlns:ns3="0c73c1f5-50cd-4477-a315-44bef7b8a847" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7966d967ae6f075ad6e4da9e3740ee6a" ns2:_="" ns3:_="">
     <xsd:import namespace="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
@@ -19304,15 +19432,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5FF01DA-2B78-4B7A-B1AA-70E314783689}">
   <ds:schemaRefs>
@@ -19325,6 +19444,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{524F9E4F-126F-4ECE-B048-66FBB2C5F2D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47248BE5-CA7E-45BD-8210-D93116D78423}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19341,12 +19468,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{524F9E4F-126F-4ECE-B048-66FBB2C5F2D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>